--- a/data/trans_orig/IP16A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58718</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36747</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37715</t>
+          <t>38082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78121</t>
+          <t>77922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82362</t>
+          <t>82360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55618</t>
+          <t>55399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>35360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59679</t>
+          <t>59608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119513</t>
+          <t>119409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124705</t>
+          <t>124708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136278</t>
+          <t>136200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142716</t>
+          <t>142702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259255</t>
+          <t>259897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266769</t>
+          <t>266763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47734</t>
+          <t>47702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97976</t>
+          <t>98696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48079</t>
+          <t>48603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91219</t>
+          <t>91832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45065</t>
+          <t>45159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49306</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92734</t>
+          <t>92687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99352</t>
+          <t>99365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179274</t>
+          <t>179389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>186176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184212</t>
+          <t>184876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190761</t>
+          <t>190787</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367557</t>
+          <t>367407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375823</t>
+          <t>375844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50281</t>
+          <t>50164</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99699</t>
+          <t>100079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31308</t>
+          <t>31784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61571</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65808</t>
+          <t>65803</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77098</t>
+          <t>76807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158630</t>
+          <t>158493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142523</t>
+          <t>143058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147533</t>
+          <t>147541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304363</t>
+          <t>304097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309548</t>
+          <t>309554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP16A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>553</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2290</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28121</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26351</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28121</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>26053</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>89</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1252</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4104</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3869</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3224</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40713</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37996</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40395</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37543</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37778</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40713</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>38082</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>126</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77922</t>
+          <t>78047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4446</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1367</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4116</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33756</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30677</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33756</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>31007</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>94</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55399</t>
+          <t>55562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3472</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3658</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3457</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1491</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4886</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38117</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35345</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24886</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22476</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22019</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>85,75%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38117</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35360</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>88</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59608</t>
+          <t>59953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7061</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7719</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>140706</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136858</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142735</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>123262</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>119409</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>124708</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>119628</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>124709</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>140706</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136200</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259897</t>
+          <t>259418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266763</t>
+          <t>266614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2787,42 +2787,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>41042</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2900,52 +2900,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4035</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4634</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4685</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1331</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4004</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>50406</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47702</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>47103</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>148</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98696</t>
+          <t>98015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50621</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48519</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>50621</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>48603</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>146</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91832</t>
+          <t>92102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5408</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5625</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4910</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5496</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47881</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44533</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>49167</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45159</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45874</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>90,33%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>47881</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>44445</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49281</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>130</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92687</t>
+          <t>92482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>99305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6824</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7603</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6602</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>188811</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>184654</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>190789</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>184045</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179389</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>186176</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>179729</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>186194</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>188811</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>184876</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>190787</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367407</t>
+          <t>367090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375844</t>
+          <t>375839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32064</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3254</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3505</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>52801</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50164</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>49497</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>159</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100079</t>
+          <t>99674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2164</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31160</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28551</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>33424</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31784</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31393</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,46%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,47%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31160</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28374</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>105</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61795</t>
+          <t>61728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65803</t>
+          <t>65801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3582</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3351</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3569</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36624</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33581</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>36624</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33688</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,39%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>110</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76807</t>
+          <t>77025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4043</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>146266</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>142594</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147536</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>161395</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>158493</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>158585</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>146266</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>143058</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147541</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304097</t>
+          <t>304219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309554</t>
+          <t>309613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
